--- a/data_extactor/batch_10_fa/batch_0063_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0063_fa.xlsx
@@ -513,22 +513,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بینایی نزدیک | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص گفتار | سهولت در کار با اعداد | استدلال ریاضی | وضوح گفتار | درک کتبی | چالاکی انگشتان | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | ثبات دست و بازو</t>
+          <t>درک شفاهی | بینایی نزدیک | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص گفتار | توانایی عددی | استدلال ریاضی | وضوح گفتار | درک کتبی | مهارت انگشتان | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>تماس با دیگران | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون گروه‌ها | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان | صرف زمان به صورت ایستاده | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | داخل ساختمان، محیط کنترل‌شده | مکالمات تلفنی | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها</t>
+          <t>ارتباط با دیگران | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت تکرار وظایف یکسان | صرف زمان برای ایستادن | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | صندوق‌داران | تعمیرکاران و سرویس‌کاران سکه، دستگاه‌های فروش خودکار و تفریحی | کارمندان باجه و اجاره | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان دفتری | کاربران ورود داده | سرپرستان خط مقدم کارکنان خدمات قماربازی | کارکنان قفس قماربازی | دیلرهای قماربازی | مدیران قماربازی | ماموران نظارت بر قماربازی و بازرسان قماربازی | نویسندگان و دوندگان کتاب‌های ورزشی و قماربازی | کارمندان پذیرش هتل، متل و اقامتگاه | کارمندان پست و اپراتورهای دستگاه‌های پست، به جز خدمات دولتی | کارمندان حساب‌های جدید | کارمندان دفتری عمومی | متصدیان پذیرش و اطلاعات | کارکنان چیدمان قفسه و سفارش‌گیران | تحویل‌داران بانک</t>
+          <t>کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | صندوق‌داران | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | کارمندان باجه و اجاره | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | اپراتورهای ورود داده | سرپرستان خط اول کارگران خدمات قمار | کارکنان باجه قمارخانه | دیلرهای قمار | مدیران قماربازی | ماموران نظارت بر قمار و بازرسان قمار | نویسندگان و دوندگان دفاتر شرط‌بندی ورزشی و قمار | کارمندان پذیرش هتل، متل و اقامتگاه | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | کارمندان حساب‌های جدید | کارمندان دفتری عمومی | متصدیان پذیرش و کارمندان اطلاعات | قفسه‌چین‌ها و پرکننده‌های سفارش | تحویل‌داران</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | مانیتورینگ | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | امور اداری | فروش و بازاریابی | مدیریت و سازماندهی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | فروش و بازاریابی | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -580,12 +580,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون گروه‌ها | مکالمات تلفنی | تماس با دیگران | داخل ساختمان، محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | فراوانی تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت دقیق یا درست بودن | ایمیل | آزادی در تصمیم‌گیری | موقعیت‌های درگیری | نزدیکی فیزیکی | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت دقیق یا درست بودن | ایمیل | آزادی در تصمیم‌گیری | موقعیت‌های تعارض | نزدیکی فیزیکی | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>صندوق‌داران | دربان‌ها | نمایندگان خدمات مشتریان | فروشندگان خانه‌به‌خانه، روزنامه‌فروشان و دستفروشان خیابانی و کارکنان مرتبط | سرپرستان خط مقدم کارکنان فروش غیرخرده‌فروشی | سرپرستان خط مقدم کارکنان فروش خرده‌فروشی | کارمندان پذیرش هتل، متل و اقامتگاه | کارمندان ثبت سفارش | فروشندگان قطعات | کارمندان خدمات پستی | کارمندان تدارکات | متصدیان پذیرش و اطلاعات | فروشندگان خرده‌فروشی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | کارمندان ارسال، دریافت و موجودی کالا | کارکنان چیدمان قفسه و سفارش‌گیران | بازاریابان تلفنی | خریداران عمده و خرده، به جز محصولات کشاورزی</t>
+          <t>صندوق‌داران | کانسرج‌ها | نمایندگان خدمات مشتریان | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان رده اول کارکنان فروش خرده‌فروشی | کارمندان پذیرش هتل، متل و اقامتگاه | کارمندان ثبت سفارش | فروشندگان قطعات | کارمندان خدمات پستی | کارمندان تدارکات | متصدیان پذیرش و کارمندان اطلاعات | فروشندگان خرده‌فروشی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | بازاریابان تلفنی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | مانیتورینگ | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | فروش و بازاریابی | مدیریت و سازماندهی | امور اداری | کامپیوتر و الکترونیک | زبان انگلیسی | اقتصاد و حسابداری | تولید و فرآوری | پرسنل و منابع انسانی | ریاضیات | مکانیک</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره | اداری | رایانه و الکترونیک | زبان انگلیسی | اقتصاد و حسابداری | تولید و فرآوری | پرسنل و منابع انسانی | ریاضیات | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | چالاکی انگشتان | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | مهارت انگشتان | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | مکالمات تلفنی | آزادی در تصمیم‌گیری | ایمیل | داخل ساختمان، بدون کنترل محیطی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون گروه‌ها | داخل ساختمان، محیط کنترل‌شده | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان به صورت ایستاده | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | موقعیت‌های درگیری</t>
+          <t>ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | آزادی در تصمیم‌گیری | ایمیل | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | پیامدهای کاری و نتایج سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فراوانی تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نزدیکی فیزیکی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | موقعیت‌های تعارض</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | متصدیان خدمات خودرو و شناورها | کارمندان باجه و اجاره | فروشندگان خانه‌به‌خانه، روزنامه‌فروشان و دستفروشان خیابانی و کارکنان مرتبط | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات مرتبط | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تعمیرکاران لوازم خانگی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | کارمندان ثبت سفارش | مکانیک‌های تجهیزات فضای باز و سایر موتورهای کوچک | کارمندان تولید، برنامه‌ریزی و هماهنگی | فروشندگان خرده‌فروشی | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | کارمندان ارسال، دریافت و موجودی کالا | کارکنان چیدمان قفسه و سفارش‌گیران | مونتاژکاران تیمی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنسین‌ها و مکانیک‌های خدمات خودرو | متصدیان خدمات خودرو و شناورهای آبی | کارمندان باجه و اجاره | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تعمیرکاران لوازم خانگی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | کارمندان ثبت سفارش | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | کارمندان تولید، برنامه‌ریزی و هماهنگی | فروشندگان خرده‌فروشی | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | مونتاژکاران تیمی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,17 +674,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ASI Point of Sale | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Advanced Retail Management Systems Retail Pro | American Precision Instruments Regit | Apple Safari | Apple macOS | Attitude POS itive AccuPOS Retail | Autodesk AutoCAD | Bibase 4POS Retail | Blink | CAP Automation SellWise | Comcash ERP | CompuTant CounterPoint | CyberMatrix | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Datasym SYMFINITE | EZ Software Solutions | Eclipse IDE | نرم‌افزار تجاری Exact | Facebook | FileMaker Pro | نرم‌افزار ثبت هدیه | Google Docs | Google Drive | Google Meet | GroupMe | نرم‌افزار دستگاه‌های کامپیوتر جیبی | IBM Notes | Infocorp Computer Solutions $mart System | Infocorp Softwear/POS | Intuit QuickBooks | سیستم‌های مدیریت موجودی | LOB RetailPoint | LinkedIn | Logisoft Positive Pos System | ManageMore Cellular Manager | Master Merchant Systems Music Store | MicroBiz | Microsoft Access | Microsoft Dynamics | Microsoft Edge | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Millennium Software Atrex | Mozilla Firefox | Oracle PeopleSoft | Plexis Software Plexis POS | نرم‌افزار کتابفروشی پایانه فروش POS | نرم‌افزار قطعات و خدمات پایانه فروش POS | RiscStation POSSum | نرم‌افزار SAP | SBS Keystroke | Sage 50 Accounting | نرم‌افزار حسابداری Sage 50 | نرم‌افزار Salesforce | Semicron Systems | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Softpedia ShopInvo | نرم‌افزار پایانه فروش System3 POS | The General Store | The Retail Solution | TokenWorks Magnetic Card Reader | True North Computer Retail Plus | VeriFone PC Charge Pro | Vigilant | Visual Retail Plus | WinMan SureSell | YouTube | iQmetrix RQ4 Retail Management System</t>
+          <t>ASI Point of Sale | Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | سیستم‌های مدیریت خرده‌فروشی پیشرفته Retail Pro | American Precision Instruments Regit | Apple Safari | Apple macOS | Attitude POS itive AccuPOS Retail | Autodesk AutoCAD | Bibase 4POS Retail | Blink | CAP Automation SellWise | Comcash ERP | CompuTant CounterPoint | CyberMatrix | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Datasym SYMFINITE | EZ Software Solutions | Eclipse IDE | نرم‌افزار تجاری Exact | Facebook | FileMaker Pro | نرم‌افزار ثبت هدیه | Google Docs | Google Drive | Google Meet | GroupMe | نرم‌افزار دستگاه‌های کامپیوتر جیبی | IBM Notes | Infocorp Computer Solutions $mart System | Infocorp Softwear/POS | Intuit QuickBooks | سیستم‌های مدیریت موجودی | LOB RetailPoint | LinkedIn | Logisoft Positive Pos System | ManageMore Cellular Manager | Master Merchant Systems Music Store | MicroBiz | Microsoft Access | Microsoft Dynamics | Microsoft Edge | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Millennium Software Atrex | Mozilla Firefox | Oracle PeopleSoft | Plexis Software Plexis POS | نرم‌افزار کتابفروشی پایانه فروش POS | نرم‌افزار قطعات و خدمات پایانه فروش POS | RiscStation POSSum | نرم‌افزار SAP | SBS Keystroke | Sage 50 Accounting | نرم‌افزار حسابداری Sage 50 | نرم‌افزار Salesforce | Semicron Systems | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Softpedia ShopInvo | نرم‌افزار پایانه فروش System3 POS | The General Store | The Retail Solution | TokenWorks Magnetic Card Reader | True North Computer Retail Plus | VeriFone PC Charge Pro | Vigilant | Visual Retail Plus | WinMan SureSell | YouTube | iQmetrix RQ4 Retail Management System</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | مانیتورینگ | یادگیری فعال | نگارش | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | مشتری‌مداری و خدمات شخصی | زبان انگلیسی | مدیریت و سازماندهی | ریاضیات | امور اداری</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>تماس با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون گروه‌ها | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | داخل ساختمان، محیط کنترل‌شده | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان به صورت ایستاده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای راه رفتن یا دویدن | نزدیکی فیزیکی | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان</t>
+          <t>ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای ایستادن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای راه رفتن یا دویدن | نزدیکی فیزیکی | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | خریداران و ماموران خرید محصولات کشاورزی | صندوق‌داران | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | فروشندگان خانه‌به‌خانه، روزنامه‌فروشان و دستفروشان خیابانی و کارکنان مرتبط | سرپرستان خط مقدم کارکنان فروش خرده‌فروشی | طراحان ویترین و دکوراتورهای مغازه | کارمندان ثبت سفارش | فروشندگان قطعات | کارمندان تدارکات | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | کارمندان ارسال, دریافت و موجودی کالا | کارکنان چیدمان قفسه و سفارش‌گیران | بازاریابان تلفنی | خریداران عمده و خرده، به جز محصولات کشاورزی</t>
+          <t>نمایندگان فروش تبلیغات | خریداران و نمایندگان خرید، محصولات کشاورزی | صندوق‌داران | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | سرپرستان رده اول کارکنان فروش خرده‌فروشی | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | کارمندان ثبت سفارش | فروشندگان قطعات | کارمندان تدارکات | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | بازاریابان تلفنی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Canva | نرم‌افزار مدیریت مخاطبین | نرم‌افزار ایمیل | Facebook | FileMaker Pro | Google Ads | Google Analytics | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | QuarkXPress | نرم‌افزار Salesforce | نرم‌افزار مرورگر وب | WordPress</t>
+          <t>نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Canva | نرم‌افزار مدیریت تماس | نرم‌افزار ایمیل | Facebook | FileMaker Pro | Google Ads | Google Analytics | Microsoft Access | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | QuarkXPress | نرم‌افزار Salesforce | نرم‌افزار مرورگر وب | WordPress</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | مانیتورینگ</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | مشتری‌مداری و خدمات شخصی | زبان انگلیسی | ارتباطات و رسانه | ریاضیات | امور اداری | کامپیوتر و الکترونیک | مدیریت و سازماندهی</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | ارتباطات و رسانه | ریاضیات | اداری | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | بینایی نزدیک | اصالت | روان بودن ایده‌ها | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
+          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | بینایی نزدیک | اصالت | روانی ایده‌ها | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | تماس با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون گروه‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سطح رقابت | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | درون وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | اهمیت دقیق یا درست بودن | صرف زمان به صورت نشسته</t>
+          <t>ایمیل | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سطح رقابت | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | نامه‌ها و یادداشت‌های کتبی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران تبلیغات و ارتقای فروش | نمایندگان و مدیران برنامه‌های هنرمندان، مجریان و ورزشکاران | کارمندان باجه و اجاره | فروشندگان خانه‌به‌خانه، روزنامه‌فروشان و دستفروشان خیابانی و کارکنان مرتبط | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | طراحان ویترین و دکوراتورهای مغازه | بازرگانان آنلاین | مدیران روابط عمومی | متخصصان روابط عمومی | نمایندگان فروش املاک و مستغلات | فروشندگان خرده‌فروشی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | استراتژیست‌های بازاریابی موتورهای جستجو | بازاریابان تلفنی | خریداران عمده و خرده، به جز محصولات کشاورزی | نویسندگان و پدیدآورندگان</t>
+          <t>مدیران تبلیغات و ترویج | نمایندگان و مدیران تجاری هنرمندان، اجراکنندگان و ورزشکاران | کارمندان باجه و اجاره | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | تاجران آنلاین | مدیران روابط عمومی | متخصصان روابط عمومی | نمایندگان فروش املاک | فروشندگان خرده‌فروشی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | استراتژیست‌های بازاریابی جستجو | بازاریابان تلفنی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AMS Services AMS 360 | AMS Services AMS Sagitta | Adobe After Effects | Advantage Information Systems The Agency Advantage | Agency Master | Agency Software AgencyPro | نرم‌افزار مدیریت آژانس | Allied Financial Software Act4Advisors | Allstar Software Systems Kofax | Apple Final Cut Pro | Applied Systems The Agency Manager | Applied Systems Vision | Benefits Technology Group SalesLogix | CPU Tracker Software CPU Tracker | CoVirt VirtGate | Cygnus Software IncomeMax | DORIS FILESERVERonline | E-Z Data SmartOffice | FINEOS Insure | Facebook | Fiserv FSC Manager | G2X Agility:Insurance | GBS Agency Expert | GroupMe | سیستم کدگذاری روش‌های رایج مراقبت‌های بهداشتی HCPCS | Hoffman Computer Systems Amsoft | InStar Orion | Infospectrum Quick Insure | Insurance Systems WebWriter BackOffice | Insurance Technologies Corporation InsurancePro | Insurance Technologies ForeSight Enterprise | Insurance Technology Consultants WOW | نرم‌افزار تحلیل بیمه | نرم‌افزار نرخ‌گذاری بیمه | LIDP Consulting Services The Administrator | LinkedIn | LogMeIn GoToMeeting | MI-Assistant MI Management System | نرم‌افزار کدگذاری فرآیندهای پزشکی | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | NaviSys Front Office | North American Software Associates Eclipse | Online Database Solutions Agent Intelligence | QuickQuote QuickFile Agency Management System | Results International Systems Artius Suite | نرم‌افزار زمان‌بندی | Skywire Software Policyware | Special Agent | Tangle S Creations Your Insurance Office | Terrace Consulting AgencyInsight | Tritech Financial Systems General Insurance Management System GIMS | نرم‌افزار صدور بیمه‌نامه | United Systems and Software Individual Life and Health Administration System | Vulcan Solutions Vulcan Insurance | نرم‌افزار مرورگر وب | YouTube | Zoom | irs-aims MARS</t>
+          <t>AMS Services AMS 360 | AMS Services AMS Sagitta | Adobe After Effects | Advantage Information Systems The Agency Advantage | Agency Master | Agency Software AgencyPro | نرم‌افزار مدیریت آژانس | Allied Financial Software Act4Advisors | Allstar Software Systems Kofax | Apple Final Cut Pro | Applied Systems The Agency Manager | Applied Systems Vision | Benefits Technology Group SalesLogix | CPU Tracker Software CPU Tracker | CoVirt VirtGate | Cygnus Software IncomeMax | DORIS FILESERVERonline | E-Z Data SmartOffice | FINEOS Insure | Facebook | Fiserv FSC Manager | G2X Agility:Insurance | GBS Agency Expert | GroupMe | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Hoffman Computer Systems Amsoft | InStar Orion | Infospectrum Quick Insure | Insurance Systems WebWriter BackOffice | Insurance Technologies Corporation InsurancePro | Insurance Technologies ForeSight Enterprise | Insurance Technology Consultants WOW | نرم‌افزار تحلیل بیمه | نرم‌افزار نرخ‌گذاری بیمه | LIDP Consulting Services The Administrator | LinkedIn | LogMeIn GoToMeeting | MI-Assistant MI Management System | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | NaviSys Front Office | North American Software Associates Eclipse | Online Database Solutions Agent Intelligence | QuickQuote QuickFile Agency Management System | Results International Systems Artius Suite | نرم‌افزار زمان‌بندی | Skywire Software Policyware | Special Agent | Tangle S Creations Your Insurance Office | Terrace Consulting AgencyInsight | Tritech Financial Systems General Insurance Management System GIMS | نرم‌افزار صدور بیمه‌نامه | United Systems and Software Individual Life and Health Administration System | Vulcan Solutions Vulcan Insurance | نرم‌افزار مرورگر وب | YouTube | Zoom | irs-aims MARS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,22 +798,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | فروش و بازاریابی | زبان انگلیسی | ریاضیات | قانون و دولت | حمل‌ونقل | مدیریت و سازماندهی | آموزش و تربیت | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | ریاضیات | قانون و دولت | حمل و نقل | مدیریت و اداره | آموزش و پرورش | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | بیان کتبی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | سهولت در کار با اعداد</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | بیان کتبی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی عددی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | گفتگوهای چهره‌به‌چهره با افراد و درون گروه‌ها | فراوانی تصمیم‌گیری | تماس با دیگران | اهمیت دقیق یا درست بودن | صرف زمان به صورت نشسته | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان، محیط کنترل‌شده | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | سطح رقابت | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | درون وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده</t>
+          <t>ایمیل | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | ارتباط با دیگران | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | سطح رقابت | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ارزیابان، بررسی‌کنندگان و بازرسان خسارت بیمه | متخصصان جبران خدمات، مزایا و تجزیه و تحلیل مشاغل | تحلیل‌گران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان دفتری | مشاوران اعتباری | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | مدیران مالی | متخصصان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان دفتری پردازش خسارت و بیمه‌نامه | کارشناسان صدور بیمه‌نامه | مصاحبه‌کنندگان و کارمندان دفتری وام | مسئولان وام | تحلیل‌گران مدیریت | کارمندان حساب‌های جدید | مشاوران مالی شخصی | نمایندگان فروش املاک و مستغلات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی</t>
+          <t>تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | کارمندان پردازش بیمه و بیمه‌نامه | بیمه‌گران | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | تحلیل‌گران مدیریت | کارمندان حساب‌های جدید | مشاوران مالی شخصی | نمایندگان فروش املاک | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ADP/Vantra VOLTS | AIQ Systems TradingExpert Pro | AnalyzerXL | Aspen Graphics Technical Analysis Software | Bloomberg Professional | BondDesk Group Trader WorkStation | C++ | CQG Integrated Client | CSI Complex Systems ClientTrade | CableSoft LiveWire Trader | Calypso Technology Calypso Asset Management | Charles River Development Charles River Investment Management System | Citi The Yield Book Calculator | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار مدیریت پایگاه داده | Derivicom FinOptions XL | نرم‌افزار ایمیل | FileMaker Pro | نرم‌افزار تحلیل نیازهای مالی | سیستم‌های معاملاتی جایگزین درآمد ثابت ATS | نرم‌افزار حسابداری صندوق | FundCount Web | نرم‌افزار گرافیکی | IBM Cognos Impromptu | IBM Notes | Imagine Software Imagine Trading System | Knight BondPoint | Leading Market Technologies EXPO | LinkedIn | Linux | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | سیستم‌های تراکنش معاملاتی چندگانه | Oracle E-Business Suite Financials | Oracle Hyperion | Oracle Java | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Siebel CRM | Python | R | Realm Business Solutions INSIGHT for ARGUS | Redi Enterprise Development Redi ERM | نرم‌افزار انطباق با آژانس‌های نظارتی | نرم‌افزار SAP | Sage 50 Accounting | نرم‌افزار تحلیل فروش | Salesforce software | نرم‌افزار زمان‌بندی | SunGard MicroHedge | Telvent DTN ProphetX | The MathWorks MATLAB | Thomson Reuters Tradeweb | Tradeweb Markets Tradeweb | Trading Blox | Triple Point Commodity XL | UNIX | نرم‌افزار مرورگر وب | سیستم‌های اطلاعاتی مبتنی بر وب | سیستم‌های معاملاتی مبتنی بر وب</t>
+          <t>ADP/Vantra VOLTS | AIQ Systems TradingExpert Pro | AnalyzerXL | نرم‌افزار تحلیل فنی Aspen Graphics | Bloomberg Professional | BondDesk Group Trader WorkStation | C++ | CQG Integrated Client | CSI Complex Systems ClientTrade | CableSoft LiveWire Trader | Calypso Technology Calypso Asset Management | Charles River Development Charles River Investment Management System | Citi The Yield Book Calculator | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار مدیریت پایگاه داده | Derivicom FinOptions XL | نرم‌افزار ایمیل | FileMaker Pro | نرم‌افزار تحلیل نیازهای مالی | سیستم‌های معاملاتی جایگزین درآمد ثابت ATS | نرم‌افزار حسابداری صندوق | FundCount Web | نرم‌افزار گرافیکی | IBM Cognos Impromptu | IBM Notes | Imagine Software Imagine Trading System | Knight BondPoint | Leading Market Technologies EXPO | LinkedIn | Linux | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visual Basic | Microsoft Windows | Microsoft Word | سیستم‌های تراکنش معاملاتی چندگانه | Oracle E-Business Suite Financials | Oracle Hyperion | Oracle Java | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Siebel CRM | Python | R | Realm Business Solutions INSIGHT for ARGUS | Redi Enterprise Development Redi ERM | نرم‌افزار انطباق با آژانس‌های نظارتی | نرم‌افزار SAP | Sage 50 Accounting | نرم‌افزار تحلیل فروش | نرم‌افزار Salesforce | نرم‌افزار زمان‌بندی | SunGard MicroHedge | Telvent DTN ProphetX | The MathWorks MATLAB | Thomson Reuters Tradeweb | Tradeweb Markets Tradeweb | Trading Blox | Triple Point Commodity XL | UNIX | نرم‌افزار مرورگر وب | سیستم‌های اطلاعاتی مبتنی بر وب | سیستم‌های معاملاتی مبتنی بر وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | مانیتورینگ | یادگیری فعال | درک مطلب | سخن گفتن | نگارش | ریاضیات</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب | سخن گفتن | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | فروش و بازاریابی | کامپیوتر و الکترونیک | مدیریت و سازماندهی | قانون و دولت | امور اداری</t>
+          <t>خدمات مشتری و شخصی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | فروش و بازاریابی | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | اداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | وضوح گفتار | درک کتبی | تشخیص گفتار | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات | روان بودن ایده‌ها | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | سهولت در کار با اعداد | اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | وضوح گفتار | درک کتبی | تشخیص گفتار | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | توانایی عددی | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون گروه‌ها | تماس با دیگران | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | صرف زمان به صورت نشسته | داخل ساختمان، محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | فشار زمانی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | سطح رقابت | فشار زمانی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کارمندان دفتری کارگزاری | تحلیل‌گران هوش تجاری | تحلیل‌گران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان دفتری | مشاوران اعتباری | مدیران مالی | متخصصان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | نمایندگان فروش بیمه | مدیران صندوق‌های سرمایه‌گذاری | مسئولان وام | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | کارمندان حساب‌های جدید | مشاوران مالی شخصی | ماموران خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | کارگزاران املاک و مستغلات | نمایندگان فروش املاک و مستغلات | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | تحویل‌داران بانک | خریداران عمده و خرده، به جز محصولات کشاورزی</t>
+          <t>کارمندان کارگزاری | تحلیلگران هوش تجاری | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | نمایندگان فروش بیمه | مدیران صندوق سرمایه‌گذاری | مسئولان وام | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | کارمندان حساب‌های جدید | مشاوران مالی شخصی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | کارگزاران املاک | نمایندگان فروش املاک | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | تحویل‌داران | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Amadeus CRS | Apollo Reservation System | Colibripms Software Colibri | DataSwell | Galor Travel Booster | نرم‌افزار سیستم توزیع جهانی GDS | Globekey Agentkey | IMS Travel Agent Reservation Software System | Illusions Online Illusions OnDemand | Intuit QuickBooks | MGHworld Travel Agents | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Orbitz Worldwide Orbitz for Agents | Rezdy booking software | Rezgo online booking software | Rezopia | SAP Concur | Sabre Airline Solutions SabreSonic Customer Sales &amp; Service | Sabre Central Command | TourCMS | TourWriter | Travel Agent CMS | TravelCarma | Travii reservation system software | Zoom</t>
+          <t>Amadeus CRS | Apollo Reservation System | Colibripms Software Colibri | DataSwell | Galor Travel Booster | نرم‌افزار سیستم توزیع جهانی GDS | Globekey Agentkey | IMS Travel Agent Reservation Software System | Illusions Online Illusions OnDemand | Intuit QuickBooks | MGHworld Travel Agents | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Orbitz Worldwide Orbitz for Agents | Rezdy booking software | Rezgo online booking software | Rezopia | SAP Concur | Sabre Airline Solutions SabreSonic Customer Sales &amp; Service | Sabre Central Command | TourCMS | TourWriter | سیستم مدیریت محتوای آژانس مسافرتی | TravelCarma | Travii reservation system software | Zoom</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | مانیتورینگ</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | فروش و بازاریابی | جغرافیا | کامپیوتر و الکترونیک | مخابرات | امور اداری | حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی | جغرافیا | رایانه و الکترونیک | مخابرات | اداری | حمل و نقل</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تشخیص گفتار | درک شفاهی | وضوح گفتار | درک کتبی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توجه انتخابی | استدلال قیاسی | بیان کتبی | روان بودن ایده‌ها | سهولت در کار با اعداد | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | اصالت</t>
+          <t>تشخیص گفتار | درک شفاهی | وضوح گفتار | درک کتبی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توجه انتخابی | استدلال قیاسی | بیان کتبی | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | اصالت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | صرف زمان به صورت نشسته | اهمیت دقیق یا درست بودن | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | گفتگوهای چهره‌به‌چهره با افراد و درون گروه‌ها | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | میزان اتوماسیون | فراوانی تصمیم‌گیری | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>مکالمات تلفنی | ایمیل | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | میزان خودکارسازی | فراوانی تصمیم‌گیری | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | نمایندگان باربری و حمل‌ونقل | دربان‌ها | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | کارگزاران گمرک | فروشندگان خانه‌به‌خانه، روزنامه‌فروشان و دستفروشان خیابانی و کارکنان مرتبط | متصدیان ارسال کالا | کارمندان پذیرش هتل، متل و اقامتگاه | نمایندگان فروش بیمه | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | نمایندگان فروش املاک و مستغلات | متصدیان پذیرش و اطلاعات | نمایندگان رزرو و بلیط حمل‌ونقل و کارمندان سفر | فروشندگان خرده‌فروشی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | بازاریابان تلفنی | اپراتورهای تلفن | راهنمایان تور و همراهان | راهنمایان سفر</t>
+          <t>نمایندگان فروش تبلیغات | نمایندگان بار و محموله | کانسرج‌ها | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | کارگزاران گمرک | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | متصدیان حمل و نقل | کارمندان پذیرش هتل، متل و اقامتگاه | نمایندگان فروش بیمه | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | نمایندگان فروش املاک | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | فروشندگان خرده‌فروشی | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | بازاریابان تلفنی | اپراتورهای تلفن | راهنمایان تور و همراهان | راهنمایان سفر</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | مانیتورینگ | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | مشتری‌مداری و خدمات شخصی | زبان انگلیسی | مدیریت و سازماندهی | اقتصاد و حسابداری | ارتباطات و رسانه | کامپیوتر و الکترونیک | ریاضیات</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | اقتصاد و حسابداری | ارتباطات و رسانه | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | چالاکی انگشتان | چالاکی دستی | بینایی دور | حفظ کردن | روان بودن ایده‌ها | بیان کتبی | اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | بیان کتبی | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون گروه‌ها | داخل ساختمان، محیط کنترل‌شده | صرف زمان به صورت نشسته | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | سطح رقابت | سخنرانی عمومی | درون وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت | سخنرانی عمومی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | کارمندان دفتری کارگزاری | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | سرپرستان خط مقدم کارکنان فروش غیرخرده‌فروشی | نمایندگان فروش بیمه | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | کارمندان حساب‌های جدید | مشاوران مالی شخصی | متخصصان روابط عمومی | ماموران خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مهندسان فروش | مدیران فروش | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازاریابان تلفنی | خریداران عمده و خرده، به جز محصولات کشاورزی</t>
+          <t>نمایندگان فروش تبلیغات | کارمندان کارگزاری | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | نمایش‌دهندگان و تبلیغ‌کنندگان محصول | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | نمایندگان فروش بیمه | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | کارمندان حساب‌های جدید | مشاوران مالی شخصی | متخصصان روابط عمومی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مهندسان فروش | مدیران فروش | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازاریابان تلفنی | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AMG Teleran SalesInSync | Act! | ActionWare | AdTrack Customer Acquisition Management CAM | نرم‌افزار Amazon Web Services AWS | Apache Hadoop | Cegedim Target Software Target SFA Pharmaceutical Suite | نرم‌افزار رایانش ابری Citrix | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | FileMaker Pro | Google Ads | Google Analytics | نرم‌افزار Google Workspace | HEAT Software GoldMine | نرم‌افزار HubSpot | IBM InfoSphere DataStage | IBM Notes | IBM SPSS Statistics | Infor ERP SyteLine | InsideSales.com | Intuit QuickBooks | Khameleon | LexisNexis | LinkedIn | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | McAfee | MicroStrategy | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Word | NetSuite ERP | NetSuite NetCRM | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Database | Oracle Fusion Applications | Oracle Hyperion | Oracle PeopleSoft | R | SAP Sybase SQL Anywhere | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Salesforce.com Salesforce CRM | نرم‌افزار زمان‌بندی | StataCorp Stata | نرم‌افزار مالیات | Teradata Database | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم پروتکل انتقال صدا از طریق اینترنت VoIP | نرم‌افزار مرورگر وب | YouTube | Zoom</t>
+          <t>AMG Teleran SalesInSync | Act! | ActionWare | AdTrack Customer Acquisition Management CAM | نرم‌افزار Amazon Web Services AWS | Apache Hadoop | Cegedim Target Software Target SFA Pharmaceutical Suite | نرم‌افزار رایانش ابری Citrix | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | FileMaker Pro | Google Ads | Google Analytics | نرم‌افزار Google Workspace | HEAT Software GoldMine | نرم‌افزار HubSpot | IBM InfoSphere DataStage | IBM Notes | IBM SPSS Statistics | Infor ERP SyteLine | InsideSales.com | Intuit QuickBooks | Khameleon | LexisNexis | LinkedIn | Linux | LogMeIn GoToMeeting | LogMeIn GoToWebinar | McAfee | MicroStrategy | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Word | NetSuite ERP | NetSuite NetCRM | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Database | Oracle Fusion Applications | Oracle Hyperion | Oracle PeopleSoft | R | SAP Sybase SQL Anywhere | نرم‌افزار SAP | SAS | نرم‌افزار Salesforce | Salesforce.com Salesforce CRM | نرم‌افزار زمان‌بندی | StataCorp Stata | نرم‌افزار مالیاتی | Teradata Database | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار مرورگر وب | YouTube | Zoom</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | تفکر انتقادی | مانیتورینگ</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | مدیریت و سازماندهی | ریاضیات | تولید و فرآوری | کامپیوتر و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | مدیریت و اداره | ریاضیات | تولید و فرآوری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | بینایی نزدیک | حساسیت به مسئله | روان بودن ایده‌ها | ترتیب‌دهی اطلاعات | استدلال استقرایی | اصالت | حفظ کردن | انعطاف‌پذیری دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | بینایی نزدیک | حساسیت به مسئله | روانی ایده‌ها | ترتیب‌دهی اطلاعات | استدلال استقرایی | اصالت | حفظ کردن | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | تماس با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون گروه‌ها | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | داخل ساختمان، محیط کنترل‌شده | نامه‌ها و یادداشت‌های کتبی | درون وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | موقعیت‌های درگیری | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>ایمیل | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | محیط داخلی، دارای کنترل شرایط محیطی | نامه‌ها و یادداشت‌های کتبی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | فروشندگان خانه‌به‌خانه، روزنامه‌فروشان و دستفروشان خیابانی و کارکنان مرتبط | سرپرستان خط مقدم کارکنان فروش غیرخرده‌فروشی | مهندسان صنایع | مدیران تولید صنعتی | متخصصان لجستیک | فروشندگان قطعات | کارمندان تولید، برنامه‌ریزی و هماهنگی | ماموران خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | فروشندگان خرده‌فروشی | مهندسان فروش | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش و ارزیابان خورشیدی | مدیران زنجیره تامین | خریداران عمده و خرده، به جز محصولات کشاورزی</t>
+          <t>نمایندگان فروش تبلیغات | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | مهندسان صنایع | مدیران تولید صنعتی | لجستیسین‌ها | فروشندگان قطعات | کارمندان تولید، برنامه‌ریزی و هماهنگی | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | فروشندگان خرده‌فروشی | مهندسان فروش | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان و ارزیابان فروش تجهیزات خورشیدی | مدیران زنجیره تأمین | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0063_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0063_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | تشخیص گفتار | محاسبات عددی | استدلال ریاضی | وضوح گفتار | درک کتبی | چابکی انگشتان | سرعت ادراک | استدلال استقرایی | استدلال قیاسی | ثبات دست و بازو</t>
+          <t>درک شفاهی | بینایی نزدیک | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص گفتار | توانایی عددی | استدلال ریاضی | وضوح گفتار | درک کتبی | مهارت انگشتان | سرعت ادراکی | استدلال استقرایی | استدلال قیاسی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان و متصدیان صدور و ثبت صورت‌حساب | کارشناسان و متصدیان حسابداری و حسابرسی | صندوق‌داران | تعمیرکاران و تکنسین‌های نگهداری دستگاه‌های سکه‌ای و فروش خودکار | متصدیان پذیرش و باجه اجاره خدمات | کارشناسان بررسی و تایید اعتبار مشتریان | کاربران ورود داده‌ها | سرپرستان رده‌اول کارکنان خدمات تفریحی و بازی | کارکنان بخش خزانه‌داری مراکز بازی | مجریان و بازی‌گردانان مراکز تفریحی | مدیران مراکز تفریحی و بازی | افسران نظارت و بازرسان مراکز بازی | نویسندگان و متصدیان ثبت شرط‌بندی‌ها | متصدیان پذیرش هتل، متل و مجتمع‌های اقامتی | متصدیان تفکیک و توزیع مرسولات | متصدیان افتتاح حساب جدید | کارمندان عمومی امور دفتری | متصدیان پذیرش و پاسخگویی اطلاعات | متصدیان چیدمان و آماده‌سازی سفارش‌ها | تحویل‌داران بانکی</t>
+          <t>کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | صندوق‌داران | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | متصدیان باجه و کرایه کالا و خدمات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | متصدیان ورود اطلاعات و داده‌آمایی | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | متصدیان باجه و خزانه‌داری مراکز بازی و سرگرمی | گردانندگان بازی‌های میزی و کازینویی | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | متصدیان ثبت و پرداخت شرط‌بندی‌های ورزشی و سرگرمی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | متصدیان افتتاح حساب | متصدیان امور دفتری و امور عمومی اداری | متصدیان پذیرش و اطلاعات | متصدیان چیدمان و آماده‌سازی سفارش | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | فروش و بازاریابی | مدیریت و امور اداری | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | فروش و بازاریابی | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات | حساسیت به مسئله | توجه انتخابی | بیان کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | توجه انتخابی | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>صندوق‌داران | راهنمایان و مسئولان خدمات تشریفات و اقامت (Concierge) | کارشناسان خدمات پس از فروش و امور مشتریان | بازاریابان و فروشندگان حضوری، دوره‌گرد و دست‌فروشان | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول فروشگاه‌های خرده‌فروشی | متصدیان پذیرش هتل، متل و مجتمع‌های اقامتی | کارشناسان ثبت و پیگیری سفارش‌ها | فروشندگان قطعات و لوازم یدکی | متصدیان باجه‌های خدمات پستی | کارشناسان تدارکات و امور خرید | متصدیان پذیرش و پاسخگویی اطلاعات | فروشندگان خرده‌فروشی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و صنعتی (کالاهای غیرفنی و غیرعلمی) | کارشناسان فروش عمده و صنعتی (کالاهای فنی و علمی) | کارشناسان انبارداری، دریافت، ارسال و کنترل موجودی | متصدیان چیدمان و آماده‌سازی سفارش‌ها | بازاریابان تلفنی | خریداران و کارشناسان خرید عمده و خرد (به‌جز محصولات کشاورزی)</t>
+          <t>صندوق‌داران | متصدیان تشریفات و خدمات میهمانان | کارشناسان خدمات و پشتیبانی مشتریان | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان ثبت و پیگیری سفارش‌ها | فروشندگان قطعات و لوازم یدکی | متصدیان باجه و امور پستی | کارمندان تدارکات و کارپردازی | متصدیان پذیرش و اطلاعات | فروشندگان خرده‌فروشی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | کارشناسان بازاریابی تلفنی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | مدیریت و امور اداری | امور اداری و دفتری | رایانه و الکترونیک | زبان انگلیسی | اقتصاد و حسابداری | تولید و فرآوری | مدیریت منابع انسانی و امور پرسنلی | ریاضیات | امور فنی و مکانیک</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره | اداری | رایانه و الکترونیک | زبان انگلیسی | اقتصاد و حسابداری | تولید و فرآوری | پرسنل و منابع انسانی | ریاضیات | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | تشخیص گفتار | درک کتبی | وضوح گفتار | مرتب‌سازی اطلاعات | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | انعطاف‌پذیری در دسته‌بندی | استدلال قیاسی | چابکی انگشتان | توجه انتخابی | سرعت ادراک | درک الگوهای ناقص</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | درک کتبی | وضوح گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | مهارت انگشتان | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هوایی | تکنسین‌ها و تعمیرکاران خودرو | کارگران و متصدیان خدمات خودرو و شناورهای سبک | متصدیان باجه و کرایه کالا و خدمات | بازاریابان و فروشندگان حضوری، دوره‌گرد و دست‌فروشان | تعمیرکاران الکتروموتور، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و ماشین‌آلات صنعتی | تعمیرکاران لوازم خانگی | کارگران ساده جابه‌جایی بار و انبارداری دستی | تکنسین‌ها و مکانیک‌های قایق‌های موتوری | کارشناسان ثبت و پیگیری سفارش‌ها | مکانیک‌های ابزارهای موتوری فضای باز و موتورهای کوچک | کارشناسان برنامه‌ریزی، پیگیری و هماهنگی تولید | فروشندگان خرده‌فروشی | کارشناسان فروش عمده و صنعتی (کالاهای غیرفنی و غیرعلمی) | کارشناسان فروش عمده و صنعتی (کالاهای فنی و علمی) | کارشناسان انبارداری، دریافت، ارسال و کنترل موجودی | متصدیان چیدمان و آماده‌سازی سفارش‌ها | کارگران گروه‌های مونتاژکاری</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مکانیک و تکنسین خدمات خودرو | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | متصدیان باجه و کرایه کالا و خدمات | بازاریابان حضوری و فروشندگان خیابانی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تعمیرکاران لوازم خانگی | کارگران جابه‌جایی دستی بار، کالا و مصالح | مکانیک و تکنسین شناورهای موتوری | متصدیان ثبت و پیگیری سفارش‌ها | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | فروشندگان خرده‌فروشی | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | مونتاژکاران گروهی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | ریاضیات | امور اداری و دفتری</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات | بیان کتبی | درک کتبی</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارشناسان فروش فضاهای تبلیغاتی | خریداران و کارشناسان تامین محصولات کشاورزی | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات پس از فروش و امور مشتریان | مجریان معرفی و تبلیغ میدانی کالاها (پروموتر) | بازاریابان و فروشندگان حضوری، دوره‌گرد و دست‌فروشان | سرپرستان رده‌اول فروشگاه‌های خرده‌فروشی | طراحان چیدمان و دکوراسیون ویترین فروشگاه‌ها | کارشناسان ثبت و پیگیری سفارش‌ها | فروشندگان قطعات و لوازم یدکی | کارشناسان تدارکات و امور خرید | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و صنعتی (کالاهای غیرفنی و غیرعلمی) | کارشناسان فروش عمده و صنعتی (کالاهای فنی و علمی) | کارشناسان انبارداری، دریافت، ارسال و کنترل موجودی | متصدیان چیدمان و آماده‌سازی سفارش‌ها | بازاریابان تلفنی | خریداران و کارشناسان خرید عمده و خرد (به‌جز محصولات کشاورزی)</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | خریداران و کارشناسان خرید محصولات کشاورزی | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول فروشندگان خرده‌فروشی | طراحان دکوراسیون و ویترین مغازه | متصدیان ثبت و پیگیری سفارش‌ها | فروشندگان قطعات و لوازم یدکی | کارمندان تدارکات و کارپردازی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | کارشناسان بازاریابی تلفنی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ارتباطات و رسانه | ریاضیات | امور اداری و دفتری | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | ارتباطات و رسانه | ریاضیات | اداری | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | دید نزدیک | ابتکار و اصالت | روانی و سیالی ایده‌ها | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات</t>
+          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | بینایی نزدیک | اصالت | روانی ایده‌ها | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران تبلیغات و روابط عمومی | مدیران برنامه و کارگزاران هنرمندان و ورزشکاران | متصدیان باجه و کرایه کالا و خدمات | بازاریابان و فروشندگان حضوری، دوره‌گرد و دست‌فروشان | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | طراحان چیدمان و دکوراسیون ویترین فروشگاه‌ها | گردانندگان و مدیران فروشگاه‌های اینترنتی | مدیران روابط عمومی | کارشناسان روابط عمومی | مشاوران و کارشناسان معاملات املاک | فروشندگان خرده‌فروشی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و صنعتی (کالاهای غیرفنی و غیرعلمی) | کارشناسان فروش عمده و صنعتی (کالاهای فنی و علمی) | استراتژیست‌های بازاریابی موتورهای جستجو | بازاریابان تلفنی | خریداران و کارشناسان خرید عمده و خرد (به‌جز محصولات کشاورزی) | نویسندگان و مولفان</t>
+          <t>مدیران تبلیغات و روابط ترویجی | مدیران برنامه‌ها و نمایندگان هنرمندان، مجریان و ورزشکاران | متصدیان باجه و کرایه کالا و خدمات | بازاریابان حضوری و فروشندگان خیابانی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | طراحان دکوراسیون و ویترین مغازه | کارشناسان تجارت الکترونیک و فروشگاه‌های اینترنتی | مدیران روابط عمومی | کارشناسان روابط عمومی | مشاوران و کارشناسان فروش املاک | فروشندگان خرده‌فروشی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | کارشناسان بازاریابی تلفنی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | زبان انگلیسی | ریاضیات | حقوق و مقررات دولتی | امور حمل‌ونقل | مدیریت و امور اداری | آموزش و تدریس | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | ریاضیات | قانون و دولت | حمل و نقل | مدیریت و اداره | آموزش و پرورش | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | بیان کتبی | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال ریاضی | انعطاف‌پذیری در دسته‌بندی | محاسبات عددی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | وضوح گفتار | بیان کتبی | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی عددی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان ارزیابی، بررسی و خسارت بیمه | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | تحلیل‌گران اعتباری | کارشناسان بررسی و تایید اعتبار مشتریان | مشاوران اعتباری و مالی | کارشناسان خدمات پس از فروش و امور مشتریان | کارشناسان مصاحبه و تعیین شرایط برنامه‌های حمایتی دولتی | مدیران مالی | کارشناسان تحلیل ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان صدور و رسیدگی به خسارت‌های بیمه | کارشناسان صدور و ارزیابی ریسک بیمه‌نامه (آندروایتر) | متصدیان پذیرش و بررسی پرونده‌های تسهیلات | کارشناسان اعطای تسهیلات و وام | تحلیل‌گران فرآیندها و ساختار سازمانی | متصدیان افتتاح حساب جدید | مشاوران مالی شخصی | مشاوران و کارشناسان معاملات املاک | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی</t>
+          <t>کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | مدیران امور مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | کارشناسان تحلیل مدیریت و روش‌ها | متصدیان افتتاح حساب | مشاوران مالی فردی | مشاوران و کارشناسان فروش املاک | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب | سخن گفتن | نگارش | ریاضیات</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب | سخن گفتن | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | فروش و بازاریابی | رایانه و الکترونیک | مدیریت و امور اداری | حقوق و مقررات دولتی | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | فروش و بازاریابی | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | اداری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | وضوح گفتار | درک کتبی | تشخیص گفتار | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | دید نزدیک | مرتب‌سازی اطلاعات | روانی و سیالی ایده‌ها | انعطاف‌پذیری در دسته‌بندی | استدلال ریاضی | محاسبات عددی | ابتکار و اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | وضوح گفتار | درک کتبی | تشخیص گفتار | حساسیت به مسئله | بیان کتبی | استدلال استقرایی | بینایی نزدیک | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | توانایی عددی | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان امور اداری کارگزاری‌ها | تحلیل‌گران هوش تجاری | تحلیل‌گران اعتباری | کارشناسان بررسی و تایید اعتبار مشتریان | مشاوران اعتباری و مالی | مدیران مالی | کارشناسان تحلیل ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان فروش بیمه | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان اعطای تسهیلات و وام | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | متصدیان افتتاح حساب جدید | مشاوران مالی شخصی | کارشناسان تدارکات و خرید (به‌جز محصولات کشاورزی) | کارگزاران املاک و مستغلات | مشاوران و کارشناسان معاملات املاک | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | تحویل‌داران بانکی | خریداران و کارشناسان خرید عمده و خرد (به‌جز محصولات کشاورزی)</t>
+          <t>کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران هوش تجاری | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | مدیران امور مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | نمایندگان و کارشناسان فروش بیمه | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان و مسئولان تسهیلات و اعتبارات | کارشناسان تحلیل تحقیقات بازار و بازاریابی | متصدیان افتتاح حساب | مشاوران مالی فردی | کارشناسان خرید و امور قراردادها | کارگزاران و مدیران معاملات املاک | مشاوران و کارشناسان فروش املاک | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | تحویل‌داران و متصدیان امور بانکی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی | جغرافیا | رایانه و الکترونیک | مخابرات و ارتباطات | امور اداری و دفتری | امور حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی | جغرافیا | رایانه و الکترونیک | مخابرات | اداری | حمل و نقل</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تشخیص گفتار | درک شفاهی | وضوح گفتار | درک کتبی | بیان شفاهی | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | توجه انتخابی | استدلال قیاسی | بیان کتبی | روانی و سیالی ایده‌ها | محاسبات عددی | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی | ابتکار و اصالت</t>
+          <t>تشخیص گفتار | درک شفاهی | وضوح گفتار | درک کتبی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توجه انتخابی | استدلال قیاسی | بیان کتبی | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | اصالت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کارشناسان فروش فضاهای تبلیغاتی | متصدیان باربری و حمل‌ونقل کالا | راهنمایان و مسئولان خدمات تشریفات و اقامت (Concierge) | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات پس از فروش و امور مشتریان | کارگزاران امور گمرکی (حق‌العمل‌کاران گمرک) | بازاریابان و فروشندگان حضوری، دوره‌گرد و دست‌فروشان | فورواردرها و متصدیان هماهنگی حمل‌ونقل کالا | متصدیان پذیرش هتل، متل و مجتمع‌های اقامتی | کارشناسان فروش بیمه | برنامه‌ریزان همایش‌ها، نشست‌ها و رویدادها | مشاوران و کارشناسان معاملات املاک | متصدیان پذیرش و پاسخگویی اطلاعات | کارشناسان رزرواسیون و صدور بلیط سفر | فروشندگان خرده‌فروشی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | بازاریابان تلفنی | اپراتورهای تلفن | راهنمایان و سرپرستان تورهای گردشگری (تور لیدر) | راهنمایان محلی سفر</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | کارگزاران حمل‌ونقل و بار | متصدیان تشریفات و خدمات میهمانان | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | حق‌العمل‌کاران و کارگزاران گمرکی | بازاریابان حضوری و فروشندگان خیابانی | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | نمایندگان و کارشناسان فروش بیمه | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | مشاوران و کارشناسان فروش املاک | متصدیان پذیرش و اطلاعات | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | فروشندگان خرده‌فروشی | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان بازاریابی تلفنی | اپراتورهای تلفن | راهنمایان تور و گردشگری | راهنمایان گردشگری و تور</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | اقتصاد و حسابداری | ارتباطات و رسانه | رایانه و الکترونیک | ریاضیات</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | اقتصاد و حسابداری | ارتباطات و رسانه | رایانه و الکترونیک | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | اشتراک زمانی | چابکی انگشتان | چابکی دستی | دید دور | توانایی حفظ کردن | روانی و سیالی ایده‌ها | بیان کتبی | ابتکار و اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها | بیان کتبی | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارشناسان فروش فضاهای تبلیغاتی | متصدیان امور اداری کارگزاری‌ها | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات پس از فروش و امور مشتریان | مجریان معرفی و تبلیغ میدانی کالاها (پروموتر) | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | کارشناسان فروش بیمه | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | متصدیان افتتاح حساب جدید | مشاوران مالی شخصی | کارشناسان روابط عمومی | کارشناسان تدارکات و خرید (به‌جز محصولات کشاورزی) | مهندسان فروش | مدیران فروش | کارشناسان فروش عمده و صنعتی (کالاهای غیرفنی و غیرعلمی) | کارشناسان فروش عمده و صنعتی (کالاهای فنی و علمی) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | بازاریابان تلفنی | خریداران و کارشناسان خرید عمده و خرد (به‌جز محصولات کشاورزی)</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | کارشناسان امور اداری و معاملات کارگزاری | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | معرفی‌کنندگان و مروجان کالا | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | نمایندگان و کارشناسان فروش بیمه | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | متصدیان افتتاح حساب | مشاوران مالی فردی | کارشناسان روابط عمومی | کارشناسان خرید و امور قراردادها | مهندسان فروش | مدیران فروش | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارشناسان بازاریابی تلفنی | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | نگارش | تفکر انتقادی | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | زبان انگلیسی | مدیریت و امور اداری | ریاضیات | تولید و فرآوری | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | مدیریت و اداره | ریاضیات | تولید و فرآوری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | دید نزدیک | حساسیت به مسئله | روانی و سیالی ایده‌ها | مرتب‌سازی اطلاعات | استدلال استقرایی | ابتکار و اصالت | توانایی حفظ کردن | انعطاف‌پذیری در دسته‌بندی</t>
+          <t>بیان شفاهی | درک شفاهی | تشخیص گفتار | وضوح گفتار | درک کتبی | بیان کتبی | استدلال قیاسی | بینایی نزدیک | حساسیت به مسئله | روانی ایده‌ها | ترتیب‌دهی اطلاعات | استدلال استقرایی | اصالت | حفظ کردن | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارشناسان فروش فضاهای تبلیغاتی | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات پس از فروش و امور مشتریان | بازاریابان و فروشندگان حضوری، دوره‌گرد و دست‌فروشان | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان لجستیک و زنجیره تامین | فروشندگان قطعات و لوازم یدکی | کارشناسان برنامه‌ریزی، پیگیری و هماهنگی تولید | کارشناسان تدارکات و خرید (به‌جز محصولات کشاورزی) | مدیران خرید و تدارکات | فروشندگان خرده‌فروشی | مهندسان فروش | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و صنعتی (کالاهای غیرفنی و غیرعلمی) | کارشناسان فروش و ارزیابی سیستم‌های خورشیدی | مدیران زنجیره تامین | خریداران و کارشناسان خرید عمده و خرد (به‌جز محصولات کشاورزی)</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | بازاریابان حضوری و فروشندگان خیابانی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | مهندسان صنایع | مدیران تولید صنعتی | کارشناسان لجستیک و مدیریت زنجیره تأمین | فروشندگان قطعات و لوازم یدکی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | فروشندگان خرده‌فروشی | مهندسان فروش | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی | مدیران زنجیره تامین | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
